--- a/files/templates/Machine_Report.xlsx
+++ b/files/templates/Machine_Report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\www\vps\public_html\erp\files\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\www\vidp\public_html\erp\files\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B2799F-4249-4FF9-936F-290675BA7E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285BFC53-BB59-460A-A202-614F078E0142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$U$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$V$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Item Code</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>Fixed By</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
 </sst>
 </file>
@@ -2136,81 +2139,85 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E88686C-9756-408B-A0C1-92A9EBF8E9F3}">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="21" width="15.7109375" customWidth="1"/>
+    <col min="2" max="22" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:U1" xr:uid="{1E88686C-9756-408B-A0C1-92A9EBF8E9F3}"/>
+  <autoFilter ref="A1:V1" xr:uid="{1E88686C-9756-408B-A0C1-92A9EBF8E9F3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
